--- a/design/tables/Staff.xlsx
+++ b/design/tables/Staff.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staff" sheetId="1" r:id="R6ce16887b74e489e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staff" sheetId="1" r:id="R36a7bc9edec84e2c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,7 +17,7 @@
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="0.######"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -33,8 +33,18 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF294E43"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -51,6 +61,16 @@
         <x:fgColor rgb="FF34564C"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7EEE9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF35584D"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -58,7 +78,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -82,6 +102,20 @@
     <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -314,6 +348,9 @@
     <x:col min="28" max="28" width="22" hidden="0" customWidth="1"/>
     <x:col min="29" max="29" width="22" hidden="0" customWidth="1"/>
     <x:col min="30" max="30" width="22" hidden="0" customWidth="1"/>
+    <x:col min="31" max="31" width="28" hidden="0" customWidth="1"/>
+    <x:col min="32" max="32" width="28" hidden="0" customWidth="1"/>
+    <x:col min="33" max="33" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="48" customHeight="1">
@@ -407,6 +444,15 @@
       <x:c r="AD1" s="6" t="str">
         <x:v>角色原画宽度</x:v>
       </x:c>
+      <x:c r="AE1" s="11" t="str">
+        <x:v>解锁关卡</x:v>
+      </x:c>
+      <x:c r="AF1" s="11" t="str">
+        <x:v>定位文本键</x:v>
+      </x:c>
+      <x:c r="AG1" s="11" t="str">
+        <x:v>展示顺序</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
       <x:c r="A2" s="3" t="str">
@@ -499,6 +545,15 @@
       <x:c r="AD2" s="3" t="str">
         <x:v>client</x:v>
       </x:c>
+      <x:c r="AE2" s="11" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="AF2" s="11" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="AG2" s="11" t="str">
+        <x:v>client</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
       <x:c r="A3" s="3" t="str">
@@ -590,6 +645,15 @@
       </x:c>
       <x:c r="AD3" s="3" t="str">
         <x:v>float</x:v>
+      </x:c>
+      <x:c r="AE3" s="11" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="AF3" s="11" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="AG3" s="11" t="str">
+        <x:v>int</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="40" customHeight="1">
@@ -683,6 +747,15 @@
       <x:c r="AD4" s="6" t="str">
         <x:v>角色原画宽度</x:v>
       </x:c>
+      <x:c r="AE4" s="11" t="str">
+        <x:v>解锁关卡</x:v>
+      </x:c>
+      <x:c r="AF4" s="11" t="str">
+        <x:v>定位文本键</x:v>
+      </x:c>
+      <x:c r="AG4" s="11" t="str">
+        <x:v>展示顺序</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -775,6 +848,15 @@
       <x:c r="AD5" s="5" t="str">
         <x:v>spriteWidth</x:v>
       </x:c>
+      <x:c r="AE5" s="13" t="str">
+        <x:v>unlockLevel</x:v>
+      </x:c>
+      <x:c r="AF5" s="13" t="str">
+        <x:v>roleKey</x:v>
+      </x:c>
+      <x:c r="AG5" s="13" t="str">
+        <x:v>displayOrder</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="7" t="n">
@@ -867,6 +949,15 @@
       <x:c r="AD6" s="8" t="n">
         <x:v>73.5</x:v>
       </x:c>
+      <x:c r="AE6" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF6" s="9" t="str">
+        <x:v>staff.role.sprout</x:v>
+      </x:c>
+      <x:c r="AG6" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="7" t="n">
@@ -959,6 +1050,15 @@
       <x:c r="AD7" s="8" t="n">
         <x:v>80</x:v>
       </x:c>
+      <x:c r="AE7" s="14" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AF7" s="9" t="str">
+        <x:v>staff.role.frost</x:v>
+      </x:c>
+      <x:c r="AG7" s="14" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="7" t="n">
@@ -1051,6 +1151,15 @@
       <x:c r="AD8" s="8" t="n">
         <x:v>62.5</x:v>
       </x:c>
+      <x:c r="AE8" s="14" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AF8" s="9" t="str">
+        <x:v>staff.role.bloom</x:v>
+      </x:c>
+      <x:c r="AG8" s="14" t="n">
+        <x:v>3</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="7" t="n">
@@ -1143,6 +1252,15 @@
       <x:c r="AD9" s="8" t="n">
         <x:v>84</x:v>
       </x:c>
+      <x:c r="AE9" s="14" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="AF9" s="9" t="str">
+        <x:v>staff.role.scope</x:v>
+      </x:c>
+      <x:c r="AG9" s="14" t="n">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="7" t="n">
@@ -1235,6 +1353,15 @@
       <x:c r="AD10" s="8" t="n">
         <x:v>84</x:v>
       </x:c>
+      <x:c r="AE10" s="14" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="AF10" s="9" t="str">
+        <x:v>staff.role.spark</x:v>
+      </x:c>
+      <x:c r="AG10" s="14" t="n">
+        <x:v>5</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="7" t="n">
@@ -1327,6 +1454,15 @@
       <x:c r="AD11" s="8" t="n">
         <x:v>84</x:v>
       </x:c>
+      <x:c r="AE11" s="14" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="AF11" s="9" t="str">
+        <x:v>staff.role.ember</x:v>
+      </x:c>
+      <x:c r="AG11" s="14" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="7" t="n">
@@ -1419,6 +1555,15 @@
       <x:c r="AD12" s="8" t="n">
         <x:v>84</x:v>
       </x:c>
+      <x:c r="AE12" s="14" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="AF12" s="9" t="str">
+        <x:v>staff.role.mint</x:v>
+      </x:c>
+      <x:c r="AG12" s="14" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="7" t="n">
@@ -1510,6 +1655,15 @@
       </x:c>
       <x:c r="AD13" s="8" t="n">
         <x:v>84</x:v>
+      </x:c>
+      <x:c r="AE13" s="14" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="AF13" s="9" t="str">
+        <x:v>staff.role.fan</x:v>
+      </x:c>
+      <x:c r="AG13" s="14" t="n">
+        <x:v>8</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
